--- a/beck_with_ols_vp.xlsx
+++ b/beck_with_ols_vp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michael.a.moon\J_BECK_BIRD_NECROPY_ID\JBECK_BIRD_NECROPY_ID\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0F20BB-BD92-4A18-BF30-0F5C6AF97C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF74A993-DD7C-4BCD-B6B6-D4440C835EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20004" yWindow="-17436" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3423" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3422" uniqueCount="594">
   <si>
     <t>TRIP_CODE</t>
   </si>
@@ -2854,8 +2854,8 @@
       <c r="B12" s="3">
         <v>38698</v>
       </c>
-      <c r="C12" t="s">
-        <v>24</v>
+      <c r="C12">
+        <v>3</v>
       </c>
       <c r="D12" s="3">
         <v>38666</v>
